--- a/output/StructureDefinition-pdex-member-no-match-group.xlsx
+++ b/output/StructureDefinition-pdex-member-no-match-group.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$41</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="314">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.1</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T14:48:28-05:00</t>
+    <t>2026-03-17T22:49:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -419,7 +419,7 @@
     <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
   </si>
   <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>Each contained Patient resource SHALL be the exact Patient resource as submitted by the requester in the MemberBundle input parameter, preserving the original resource id, all identifiers, and all demographics supplied by the requester. Responders SHALL NOT abridge or modify the submitted Patient resource. Where the same patient was submitted with multiple different Coverage plans, a contained Coverage resource MAY also be included to identify which (patient + coverage) pair this member entry corresponds to.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -832,6 +832,12 @@
     <t>Group.member.entity.extension</t>
   </si>
   <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -858,7 +864,26 @@
     <t>Input Patient Parameter supplied for the individual member match (Patient Demographics).</t>
   </si>
   <si>
-    <t>Add the patient record from the failed Member Match request (Patient Demographics).</t>
+    <t>SHALL reference the contained Patient resource that was submitted by the requester for this member in the MemberBundle input parameter. This enables the requester to cross-reference each non-matched or consent-constrained result back to their original submitted demographics.</t>
+  </si>
+  <si>
+    <t>Group.member.entity.extension:nonMatchedCoverage</t>
+  </si>
+  <si>
+    <t>nonMatchedCoverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/davinci-pdex/StructureDefinition/base-ext-match-coverage}
+</t>
+  </si>
+  <si>
+    <t>Member-Match Input Coverage Parameter</t>
+  </si>
+  <si>
+    <t>Input Coverage Parameter supplied for the individual member match. When the same patient is submitted with multiple different coverage plans, this optional extension allows the responder to include the submitted Coverage resource alongside the submitted Patient resource, enabling the requester to unambiguously identify which (patient + coverage) pair each Group member entry corresponds to.</t>
+  </si>
+  <si>
+    <t>MAY reference a contained Coverage resource that was submitted alongside the Patient in the MemberBundle input parameter. SHALL be populated when the same patient was submitted with multiple different Coverage plans, to allow the requester to distinguish which (patient + coverage) pair this member entry corresponds to.</t>
   </si>
   <si>
     <t>Group.member.entity.reference</t>
@@ -1305,12 +1330,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL40"/>
+  <dimension ref="A1:AL41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.51953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.83984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.57421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
@@ -4826,11 +4851,11 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>81</v>
@@ -4848,14 +4873,12 @@
         <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>136</v>
+        <v>262</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -4892,16 +4915,16 @@
         <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>217</v>
@@ -4919,7 +4942,7 @@
         <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>214</v>
+        <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
@@ -4927,20 +4950,20 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>261</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
@@ -4955,16 +4978,16 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5035,14 +5058,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>79</v>
       </c>
@@ -5054,25 +5079,25 @@
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>186</v>
+        <v>275</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5122,22 +5147,22 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>276</v>
+        <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
@@ -5145,10 +5170,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5171,16 +5196,16 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5206,40 +5231,40 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="Z36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AA36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF36" t="s" s="2">
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI36" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>101</v>
@@ -5279,7 +5304,7 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>286</v>
@@ -5314,13 +5339,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>79</v>
+        <v>291</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -5338,7 +5363,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5353,7 +5378,7 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>290</v>
+        <v>132</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>79</v>
@@ -5361,10 +5386,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5387,16 +5412,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5446,7 +5471,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5461,7 +5486,7 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>132</v>
+        <v>298</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
@@ -5469,10 +5494,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5492,27 +5517,25 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q39" t="s" s="2">
-        <v>300</v>
-      </c>
+      <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
         <v>79</v>
       </c>
@@ -5556,7 +5579,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5571,7 +5594,7 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
@@ -5579,10 +5602,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5605,68 +5628,68 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q40" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="R40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="P40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q40" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="R40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5687,8 +5710,118 @@
         <v>79</v>
       </c>
     </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q41" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="R41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL40">
+  <autoFilter ref="A1:AL41">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5698,7 +5831,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI39">
+  <conditionalFormatting sqref="A2:AI40">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/output/StructureDefinition-pdex-member-no-match-group.xlsx
+++ b/output/StructureDefinition-pdex-member-no-match-group.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T22:49:33-04:00</t>
+    <t>2026-03-19T09:51:30-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-pdex-member-no-match-group.xlsx
+++ b/output/StructureDefinition-pdex-member-no-match-group.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:51:30-04:00</t>
+    <t>2026-03-31T21:00:10-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-pdex-member-no-match-group.xlsx
+++ b/output/StructureDefinition-pdex-member-no-match-group.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="315">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T21:00:10-04:00</t>
+    <t>2026-05-29T12:37:47-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -419,7 +419,7 @@
     <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
   </si>
   <si>
-    <t>Each contained Patient resource SHALL be the exact Patient resource as submitted by the requester in the MemberBundle input parameter, preserving the original resource id, all identifiers, and all demographics supplied by the requester. Responders SHALL NOT abridge or modify the submitted Patient resource. Where the same patient was submitted with multiple different Coverage plans, a contained Coverage resource MAY also be included to identify which (patient + coverage) pair this member entry corresponds to.</t>
+    <t>Each contained Patient resource SHALL be the Patient resource submitted by the requester in the MemberBundle input parameter, preserving the original resource id, all identifier elements, and all demographic elements (name, birthDate, gender, address, telecom, communication, and other Patient elements supplied by the requester) so that the requester can unambiguously correlate each match result back to the submitted member. Responders SHALL NOT modify, abridge, or substitute the submitted Patient resource's id, identifiers, or demographic elements. Per FHIR R4 References (http://hl7.org/fhir/R4/references.html#contained), contained resources SHALL NOT carry meta.versionId, meta.lastUpdated, or meta.security and SHALL NOT themselves contain nested contained resources; where the submitted Patient resource carries any of those base-FHIR-prohibited elements, the responder SHALL remove them when copying the resource into Group.contained[], and doing so is not considered a violation of the preservation requirement. Where the same patient was submitted with multiple different Coverage plans, a contained Coverage resource MAY also be included to identify which (patient + coverage) pair this member entry corresponds to.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -521,10 +521,10 @@
     <t>Group.type</t>
   </si>
   <si>
-    <t>person | animal | practitioner | device | medication | substance</t>
-  </si>
-  <si>
-    <t>Identifies the broad classification of the kind of resources the group includes.</t>
+    <t>Type of group (submitted members)</t>
+  </si>
+  <si>
+    <t>Fixed to 'person'. Group.member entries reference (typically contained) Patient resources representing the submitted members that could not be matched or are consent-constrained.</t>
   </si>
   <si>
     <t>Group members SHALL be of the appropriate resource type (Patient for person or animal; or Practitioner, Device, Medication or Substance for the other types.).</t>
@@ -533,6 +533,9 @@
     <t>Identifies what type of resources the group is made up of.</t>
   </si>
   <si>
+    <t>person</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -551,10 +554,10 @@
     <t>Group.actual</t>
   </si>
   <si>
-    <t>Descriptive or actual</t>
-  </si>
-  <si>
-    <t>If true, indicates that the resource refers to a specific group of real individuals.  If false, the group defines a set of intended individuals.</t>
+    <t>Actual group (not definitional)</t>
+  </si>
+  <si>
+    <t>An actual list of submitted members for whom the match failed, not a conceptual/definitional group.</t>
   </si>
   <si>
     <t>There are use-cases for groups that define specific collections of individuals, and other groups that define "types" of intended individuals.  The requirements for both kinds of groups are similar, so we use a single resource, distinguished by this flag.</t>
@@ -636,14 +639,14 @@
     <t>Group.managingEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
-    <t>Entity that is the custodian of the Group's definition</t>
-  </si>
-  <si>
-    <t>Entity responsible for defining and maintaining Group characteristics and/or registered members.</t>
+    <t>Payer managing this group</t>
+  </si>
+  <si>
+    <t>Reference to the Payer organization that created and is managing this no-match Group. Constrained to Organization since the managing entity is always a Payer (i.e., a healthcare organization), not a Practitioner, PractitionerRole, or RelatedPerson.</t>
   </si>
   <si>
     <t>This does not strictly align with ownership of a herd or flock, but may suffice to represent that relationship in simple cases. More complex cases will require an extension.</t>
@@ -2678,7 +2681,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>79</v>
@@ -2728,7 +2731,7 @@
         <v>79</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>79</v>
@@ -2743,13 +2746,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -2782,18 +2785,18 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2807,7 +2810,7 @@
         <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>79</v>
@@ -2819,14 +2822,14 @@
         <v>154</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -2836,7 +2839,7 @@
         <v>79</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>79</v>
@@ -2875,7 +2878,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>89</v>
@@ -2884,24 +2887,24 @@
         <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2924,16 +2927,16 @@
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2959,11 +2962,11 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -2981,7 +2984,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2996,18 +2999,18 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3030,17 +3033,17 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>79</v>
@@ -3089,7 +3092,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3104,7 +3107,7 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>79</v>
@@ -3112,10 +3115,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3138,19 +3141,19 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3199,7 +3202,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3214,7 +3217,7 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>79</v>
@@ -3222,10 +3225,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3248,16 +3251,16 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3307,7 +3310,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3330,10 +3333,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3356,19 +3359,19 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -3417,7 +3420,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3432,7 +3435,7 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>79</v>
@@ -3440,10 +3443,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3466,13 +3469,13 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3523,7 +3526,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3538,7 +3541,7 @@
         <v>79</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>79</v>
@@ -3546,10 +3549,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3578,7 +3581,7 @@
         <v>136</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>138</v>
@@ -3631,7 +3634,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3646,7 +3649,7 @@
         <v>140</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>79</v>
@@ -3654,14 +3657,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3683,10 +3686,10 @@
         <v>135</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>138</v>
@@ -3741,7 +3744,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3764,10 +3767,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3790,17 +3793,17 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -3825,10 +3828,10 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z23" t="s" s="2">
         <v>79</v>
@@ -3849,7 +3852,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>89</v>
@@ -3864,7 +3867,7 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>79</v>
@@ -3872,10 +3875,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3898,19 +3901,19 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -3935,10 +3938,10 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>79</v>
@@ -3959,7 +3962,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>89</v>
@@ -3974,7 +3977,7 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>79</v>
@@ -3982,10 +3985,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4011,16 +4014,16 @@
         <v>154</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4069,7 +4072,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>89</v>
@@ -4084,7 +4087,7 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>79</v>
@@ -4092,10 +4095,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4118,13 +4121,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4175,7 +4178,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4198,10 +4201,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4224,17 +4227,17 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -4283,7 +4286,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4292,13 +4295,13 @@
         <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>79</v>
@@ -4306,10 +4309,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4332,13 +4335,13 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4389,7 +4392,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4404,7 +4407,7 @@
         <v>79</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>79</v>
@@ -4412,10 +4415,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4444,7 +4447,7 @@
         <v>136</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>138</v>
@@ -4497,7 +4500,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4512,7 +4515,7 @@
         <v>140</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>79</v>
@@ -4520,14 +4523,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4549,10 +4552,10 @@
         <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>138</v>
@@ -4607,7 +4610,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4630,10 +4633,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4656,16 +4659,16 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4715,7 +4718,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>89</v>
@@ -4738,10 +4741,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4764,13 +4767,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4821,7 +4824,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4836,7 +4839,7 @@
         <v>79</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -4844,10 +4847,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4873,10 +4876,10 @@
         <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4915,19 +4918,19 @@
         <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4950,13 +4953,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
@@ -4978,16 +4981,16 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5037,7 +5040,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5060,13 +5063,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>79</v>
@@ -5088,16 +5091,16 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5147,7 +5150,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5170,10 +5173,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5196,16 +5199,16 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5255,7 +5258,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5264,7 +5267,7 @@
         <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>101</v>
@@ -5278,10 +5281,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5307,13 +5310,13 @@
         <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5339,13 +5342,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -5363,7 +5366,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5386,10 +5389,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5415,13 +5418,13 @@
         <v>147</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5471,7 +5474,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5486,7 +5489,7 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
@@ -5494,10 +5497,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5520,16 +5523,16 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5579,7 +5582,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5602,10 +5605,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5628,23 +5631,23 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R40" t="s" s="2">
         <v>79</v>
@@ -5689,7 +5692,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5712,10 +5715,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5741,20 +5744,20 @@
         <v>154</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R41" t="s" s="2">
         <v>79</v>
@@ -5799,7 +5802,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
